--- a/output/pdf_financials_xlsx/ATY.xlsx
+++ b/output/pdf_financials_xlsx/ATY.xlsx
@@ -5176,16 +5176,16 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.042429</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-0.05621</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-0.112939</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-0.715935</v>
       </c>
       <c r="H91" s="3" t="n">
         <v>0</v>
@@ -5225,46 +5225,46 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.230199</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.855575</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.92695</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.179219</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.802536</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.492376</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.623211</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.027411</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.466838</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.806985</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.479671</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>5.732939</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>5.925151</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>6.082537</v>
       </c>
     </row>
     <row r="93">
@@ -5752,10 +5752,10 @@
         <v>0</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.011092</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.185639</v>
       </c>
       <c r="E103" s="3" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0.27387</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.292937</v>
+        <v>0.281845</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.576052</v>
@@ -6532,10 +6532,10 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-1.450809</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-5.870203</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0</v>
@@ -9608,7 +9608,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -14015,7 +14019,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -17458,7 +17466,11 @@
           <t>Share-based payments reserve (Note 13)</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -17541,7 +17553,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -18635,7 +18651,11 @@
           <t>Share-based payments reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -19541,7 +19561,11 @@
           <t>Share-based payments reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -20192,7 +20216,11 @@
           <t>Share-based payments reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -38395,7 +38423,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -38755,7 +38787,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ATY.xlsx
+++ b/output/pdf_financials_xlsx/ATY.xlsx
@@ -983,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.051836</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
         <v>-0.620865</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.186438</v>
+        <v>-1.238274</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-3.064689</v>
@@ -1935,7 +1935,7 @@
         <v>-0.620865</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.186438</v>
+        <v>-1.238274</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-3.064689</v>
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.0264</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.127141</v>
@@ -2191,16 +2191,16 @@
         <v>6.014723</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>7.162475</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>14.623559</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>15.230835</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>8.298367000000001</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>3.055305</v>
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.0264</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.127141</v>
@@ -2295,16 +2295,16 @@
         <v>6.014723</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>7.162475</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>14.623559</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>15.230835</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>8.298367000000001</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>3.055305</v>
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.0264</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.011092</v>
@@ -2919,16 +2919,16 @@
         <v>0.5730189999999999</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>7.295077</v>
+        <v>0.132602</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>15.671157</v>
+        <v>1.047598</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>15.935301</v>
+        <v>0.704466</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>8.937639000000001</v>
+        <v>0.639272</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.320585</v>
@@ -10127,7 +10127,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -19656,7 +19656,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
@@ -39871,7 +39871,11 @@
           <t>General and administrative expenses 19 ### 19</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -55099,7 +55103,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -56195,7 +56199,7 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">

--- a/output/pdf_financials_xlsx/ATY.xlsx
+++ b/output/pdf_financials_xlsx/ATY.xlsx
@@ -6975,16 +6975,16 @@
         <v>-0.602745</v>
       </c>
       <c r="L126" s="3" t="n">
-        <v>0</v>
+        <v>-0.931921</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>0</v>
+        <v>-1.667015</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>0</v>
+        <v>-0.631931</v>
       </c>
       <c r="O126" s="3" t="n">
-        <v>0</v>
+        <v>-0.874106</v>
       </c>
       <c r="P126" s="3" t="n">
         <v>0</v>
@@ -22999,7 +22999,11 @@
           <t>Dividend paid to non-controlling interests - (448,207)</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -25827,7 +25831,11 @@
           <t>Dividend paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -28803,7 +28811,11 @@
           <t>Dividend paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
